--- a/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
@@ -1459,7 +1459,7 @@
       <formula2>1000000000000</formula2>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B8">
-      <formula1>"Sin cargas familiares,1 carga familiar,2 cargas familiares,3 cargas familiares,4 cargas familiares,5 o más cargas familiares"</formula1>
+      <formula1>'Tablas oficiales'!$B$4:$B$9</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B9">
       <formula1>"Sí,No"</formula1>
@@ -1750,7 +1750,7 @@
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B15">
-      <formula1>"Costa y Galápagos,Sierra y Amazonía"</formula1>
+      <formula1>'Tablas oficiales'!$B$28:$B$29</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Escribe una fecha como dd/mm/aaaa." sqref="B16:B17">
       <formula1>18264</formula1>
@@ -2138,7 +2138,7 @@
       <formula1>"Despido intempestivo (sin causa),Renuncia con aviso escrito (desahucio),Acuerdo entre las partes,Visto bueno pedido por el empleador"</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B9">
-      <formula1>"Costa y Galápagos,Sierra y Amazonía"</formula1>
+      <formula1>'Tablas oficiales'!$B$28:$B$29</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas, tu remuneración y cómo terminó la relación, y te dice el desahucio, la indemnización, los décimos pendientes y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 8/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -359,7 +359,7 @@
     <t>Tablas oficiales de Ecuador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 8/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1834,7 +1834,7 @@
         <v>76</v>
       </c>
       <c r="B6" s="22">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>77</v>

--- a/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas, tu remuneración y cómo terminó la relación, y te dice el desahucio, la indemnización, los décimos pendientes y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 13/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -359,7 +359,7 @@
     <t>Tablas oficiales de Ecuador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 13/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1834,7 +1834,7 @@
         <v>76</v>
       </c>
       <c r="B6" s="22">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>77</v>

--- a/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas, tu remuneración y cómo terminó la relación, y te dice el desahucio, la indemnización, los décimos pendientes y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -359,7 +359,7 @@
     <t>Tablas oficiales de Ecuador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1834,7 +1834,7 @@
         <v>76</v>
       </c>
       <c r="B6" s="22">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>77</v>

--- a/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas, tu remuneración y cómo terminó la relación, y te dice el desahucio, la indemnización, los décimos pendientes y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -359,7 +359,7 @@
     <t>Tablas oficiales de Ecuador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1834,7 +1834,7 @@
         <v>76</v>
       </c>
       <c r="B6" s="22">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>77</v>

--- a/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas, tu remuneración y cómo terminó la relación, y te dice el desahucio, la indemnización, los décimos pendientes y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -359,7 +359,7 @@
     <t>Tablas oficiales de Ecuador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1834,7 +1834,7 @@
         <v>76</v>
       </c>
       <c r="B6" s="22">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>77</v>

--- a/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas, tu remuneración y cómo terminó la relación, y te dice el desahucio, la indemnización, los décimos pendientes y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -359,7 +359,7 @@
     <t>Tablas oficiales de Ecuador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1834,7 +1834,7 @@
         <v>76</v>
       </c>
       <c r="B6" s="22">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>77</v>

--- a/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="168">
   <si>
     <t>Planilla de sueldo y liquidación Ecuador 2026</t>
   </si>
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas, tu remuneración y cómo terminó la relación, y te dice el desahucio, la indemnización, los décimos pendientes y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -50,12 +50,24 @@
     <t>Sueldo neto: IESS, impuesto a la renta y décimos</t>
   </si>
   <si>
+    <t>Sin cargas familiares</t>
+  </si>
+  <si>
+    <t>1 carga familiar</t>
+  </si>
+  <si>
     <t>Paso a paso</t>
   </si>
   <si>
+    <t>2 cargas familiares</t>
+  </si>
+  <si>
     <t>TUS DATOS</t>
   </si>
   <si>
+    <t>3 cargas familiares</t>
+  </si>
+  <si>
     <t>Sueldo mensual</t>
   </si>
   <si>
@@ -65,6 +77,9 @@
     <t>Aporte e impuesto a la renta</t>
   </si>
   <si>
+    <t>4 cargas familiares</t>
+  </si>
+  <si>
     <t>Cobras los décimos cada mes</t>
   </si>
   <si>
@@ -74,6 +89,9 @@
     <t>Aporte personal al IESS</t>
   </si>
   <si>
+    <t>5 o más cargas familiares</t>
+  </si>
+  <si>
     <t>Gastos personales proyectados para el año</t>
   </si>
   <si>
@@ -86,9 +104,6 @@
     <t>Cargas familiares</t>
   </si>
   <si>
-    <t>Sin cargas familiares</t>
-  </si>
-  <si>
     <t>Impuesto causado del año</t>
   </si>
   <si>
@@ -140,6 +155,12 @@
     <t>Décimo tercero y décimo cuarto</t>
   </si>
   <si>
+    <t>Costa y Galápagos</t>
+  </si>
+  <si>
+    <t>Sierra y Amazonía</t>
+  </si>
+  <si>
     <t>DÉCIMO TERCERO</t>
   </si>
   <si>
@@ -200,9 +221,6 @@
     <t>Región donde trabajas</t>
   </si>
   <si>
-    <t>Sierra y Amazonía</t>
-  </si>
-  <si>
     <t>Período: meses</t>
   </si>
   <si>
@@ -359,7 +377,7 @@
     <t>Tablas oficiales de Ecuador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -398,21 +416,6 @@
     <t>7/10/2026</t>
   </si>
   <si>
-    <t>1 carga familiar</t>
-  </si>
-  <si>
-    <t>2 cargas familiares</t>
-  </si>
-  <si>
-    <t>3 cargas familiares</t>
-  </si>
-  <si>
-    <t>4 cargas familiares</t>
-  </si>
-  <si>
-    <t>5 o más cargas familiares</t>
-  </si>
-  <si>
     <t>Aporte personal al IESS (sector privado, relación de dependencia)</t>
   </si>
   <si>
@@ -471,9 +474,6 @@
   </si>
   <si>
     <t>Mes en que empieza el período del décimo cuarto (y en cuyo día 15 vence el pago)</t>
-  </si>
-  <si>
-    <t>Costa y Galápagos</t>
   </si>
   <si>
     <t>6/5/2015</t>
@@ -1223,7 +1223,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1232,68 +1232,89 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
-    </row>
-    <row r="3" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="Z1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="5:26" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="Z3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="Z4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" s="8">
         <v>1500</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F6" s="13">
         <f>ROUND(B5*'Tablas oficiales'!$C$10/100,2)</f>
       </c>
+      <c r="Z6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B7" s="8">
         <v>0</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F7" s="13">
         <f>ROUND((B5-F6)*12,2)</f>
@@ -1301,13 +1322,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F8" s="13">
         <f>ROUND(IF(F7&lt;=0,0,INDEX('Tablas oficiales'!$E$13:$E$22,IFERROR(MATCH(F7,'Tablas oficiales'!$B$13:$B$22,1),1))+(F7-INDEX('Tablas oficiales'!$B$13:$B$22,IFERROR(MATCH(F7,'Tablas oficiales'!$B$13:$B$22,1),1)))*INDEX('Tablas oficiales'!$D$13:$D$22,IFERROR(MATCH(F7,'Tablas oficiales'!$B$13:$B$22,1),1))/100),2)</f>
@@ -1315,16 +1336,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F9" s="14">
         <f>IF(B9="Sí",'Tablas oficiales'!$C$24,INDEX('Tablas oficiales'!$C$4:$C$9,MATCH(B8,'Tablas oficiales'!$B$4:$B$9,0)))</f>
@@ -1332,7 +1353,7 @@
     </row>
     <row r="10" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E10" s="12" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F10" s="13">
         <f>ROUND('Tablas oficiales'!$C$25*F9,2)</f>
@@ -1340,12 +1361,12 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="E11" s="12" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F11" s="13">
         <f>MIN(ROUND(MIN(B7,F10)*'Tablas oficiales'!$C$26/100,2),F8)</f>
@@ -1353,13 +1374,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B12" s="16">
         <f>B5</f>
       </c>
       <c r="E12" s="12" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F12" s="13">
         <f>ROUND(F8-F11,2)</f>
@@ -1367,13 +1388,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B13" s="16">
         <f>F6</f>
       </c>
       <c r="E13" s="12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F13" s="13">
         <f>ROUND(F12/11,2)</f>
@@ -1381,13 +1402,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B14" s="16">
         <f>F13</f>
       </c>
       <c r="E14" s="12" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F14" s="13">
         <f>IF(B6="Sí",ROUND(B5/12,2),0)</f>
@@ -1395,13 +1416,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B15" s="16">
         <f>F12</f>
       </c>
       <c r="E15" s="12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F15" s="13">
         <f>IF(B6="Sí",ROUND('Tablas oficiales'!$C$27/12,2),0)</f>
@@ -1409,7 +1430,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B16" s="16">
         <f>F14</f>
@@ -1417,7 +1438,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B17" s="16">
         <f>F15</f>
@@ -1425,7 +1446,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B18" s="18">
         <f>ROUND(B5-F6-F13+F14+F15,2)</f>
@@ -1433,7 +1454,7 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1458,8 +1479,8 @@
       <formula1>0</formula1>
       <formula2>1000000000000</formula2>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B8">
-      <formula1>'Tablas oficiales'!$B$4:$B$9</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Cargas familiares)." sqref="B8">
+      <formula1>'Sueldo neto'!$Z$1:$Z$6</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B9">
       <formula1>"Sí,No"</formula1>
@@ -1475,7 +1496,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1484,29 +1505,38 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
+      <c r="Z1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="3" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="E4" s="12" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F4" s="13">
         <f>B5*B6+B7</f>
@@ -1514,41 +1544,41 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" s="8">
         <v>1000</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B6" s="19">
         <v>12</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B7" s="8">
         <v>0</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F7" s="20">
         <f>INDEX('Tablas oficiales'!$C$28:$C$29,MATCH(B15,'Tablas oficiales'!$B$28:$B$29,0))</f>
@@ -1556,13 +1586,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B8" s="16">
         <f>ROUND(F4,2)</f>
       </c>
       <c r="E8" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F8" s="21">
         <f>IF(NOT(ISNUMBER(B17)),B18,B17)</f>
@@ -1570,13 +1600,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B9" s="16">
         <f>ROUND(B5/12,2)</f>
       </c>
       <c r="E9" s="12" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F9" s="21">
         <f>DATE(IF(MONTH(F8)&gt;=F7,YEAR(F8),YEAR(F8)-1),F7,1)</f>
@@ -1584,13 +1614,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B10" s="18">
         <f>ROUND(F4/12,2)</f>
       </c>
       <c r="E10" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F10" s="21">
         <f>IF(AND(NOT(ISNUMBER(B17)),B18&lt;=DATE(YEAR(F9),F7,15)),EDATE(F9,-12),F9)</f>
@@ -1598,7 +1628,7 @@
     </row>
     <row r="11" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E11" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F11" s="21">
         <f>EDATE(F10,12)-1</f>
@@ -1606,12 +1636,12 @@
     </row>
     <row r="12" ht="21" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="E12" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F12" s="21">
         <f>IF(NOT(ISNUMBER(B17)),F11,F8)</f>
@@ -1619,7 +1649,7 @@
     </row>
     <row r="13" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E13" s="12" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F13" s="20">
         <f>IF(EDATE(MAX(B16,F10),12*(YEAR((F12+1))-YEAR(MAX(B16,F10))))&gt;(F12+1),(YEAR((F12+1))-YEAR(MAX(B16,F10)))-1,(YEAR((F12+1))-YEAR(MAX(B16,F10))))</f>
@@ -1627,12 +1657,12 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="E14" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F14" s="21">
         <f>EDATE(MAX(B16,F10),12*F13)</f>
@@ -1640,13 +1670,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F15" s="20">
         <f>MIN(12,IF(EDATE(F14,((YEAR((F12+1))-YEAR(F14))*12+MONTH((F12+1))-MONTH(F14)))&gt;(F12+1),((YEAR((F12+1))-YEAR(F14))*12+MONTH((F12+1))-MONTH(F14))-1,((YEAR((F12+1))-YEAR(F14))*12+MONTH((F12+1))-MONTH(F14))))</f>
@@ -1654,13 +1684,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B16" s="22">
         <v>45672</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F16" s="20">
         <f>(F12+1)-EDATE(F14,F15)</f>
@@ -1668,14 +1698,14 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="9" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F17" s="14">
         <f>MIN(12,F13*12+F15+F16/30)</f>
@@ -1683,13 +1713,13 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B18" s="22">
         <f>TODAY()</f>
       </c>
       <c r="C18" s="9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1701,7 +1731,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B20" s="24">
         <f>"Del "&amp;DAY(F10)&amp;"/"&amp;MONTH(F10)&amp;"/"&amp;YEAR(F10)&amp;" al "&amp;DAY(F11)&amp;"/"&amp;MONTH(F11)&amp;"/"&amp;YEAR(F11)</f>
@@ -1709,7 +1739,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B21" s="25">
         <f>ROUND(F17,2)</f>
@@ -1717,7 +1747,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B22" s="16">
         <f>ROUND('Tablas oficiales'!$C$27/12,2)</f>
@@ -1725,7 +1755,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B23" s="18">
         <f>ROUND('Tablas oficiales'!$C$27*F17/12,2)</f>
@@ -1733,7 +1763,7 @@
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1749,8 +1779,8 @@
     <mergeCell ref="A25:C25"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B15">
-      <formula1>'Tablas oficiales'!$B$28:$B$29</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Región donde trabajas)." sqref="B15">
+      <formula1>'Décimos'!$Z$1:$Z$2</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Escribe una fecha como dd/mm/aaaa." sqref="B16:B17">
       <formula1>18264</formula1>
@@ -1778,7 +1808,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1787,29 +1817,38 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
+      <c r="Z1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="3" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="E4" s="12" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F4" s="20">
         <f>IF(EDATE(B5,12*(YEAR((B6+1))-YEAR(B5)))&gt;(B6+1),(YEAR((B6+1))-YEAR(B5))-1,(YEAR((B6+1))-YEAR(B5)))</f>
@@ -1817,13 +1856,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B5" s="22">
         <v>44621</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F5" s="21">
         <f>EDATE(B5,12*F4)</f>
@@ -1831,13 +1870,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B6" s="22">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F6" s="20">
         <f>MIN(12,IF(EDATE(F5,((YEAR((B6+1))-YEAR(F5))*12+MONTH((B6+1))-MONTH(F5)))&gt;(B6+1),((YEAR((B6+1))-YEAR(F5))*12+MONTH((B6+1))-MONTH(F5))-1,((YEAR((B6+1))-YEAR(F5))*12+MONTH((B6+1))-MONTH(F5))))</f>
@@ -1845,16 +1884,16 @@
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B7" s="8">
         <v>900</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F7" s="20">
         <f>(B6+1)-EDATE(F5,F6)</f>
@@ -1862,32 +1901,32 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F10" s="13">
         <f>IF(B8&lt;&gt;"Visto bueno pedido por el empleador",ROUND(B7*'Tablas oficiales'!$C$30/100*F4,2),0)</f>
@@ -1895,13 +1934,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B11" s="19">
         <v>0</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F11" s="20">
         <f>IF(B8="Despido intempestivo (sin causa)",IF(OR(F4&lt;'Tablas oficiales'!$C$31,AND(F4='Tablas oficiales'!$C$31,NOT(OR(F6&gt;0,F7&gt;0)))),'Tablas oficiales'!$C$32,MIN(F4+IF(OR(F6&gt;0,F7&gt;0),1,0),'Tablas oficiales'!$C$33)),0)</f>
@@ -1909,7 +1948,7 @@
     </row>
     <row r="12" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E12" s="12" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F12" s="13">
         <f>ROUND(B7*F11,2)</f>
@@ -1917,7 +1956,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1929,18 +1968,18 @@
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
       <c r="E14" s="10" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B15" s="24">
         <f>F4&amp;" años, "&amp;F6&amp;" meses y "&amp;F7&amp;" días"</f>
       </c>
       <c r="E15" s="12" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F15" s="20">
         <f>IF(EDATE(MAX(B5,DATE(IF(MONTH(B6)&gt;=12,YEAR(B6),YEAR(B6)-1),12,1)),12*(YEAR((B6+1))-YEAR(MAX(B5,DATE(IF(MONTH(B6)&gt;=12,YEAR(B6),YEAR(B6)-1),12,1)))))&gt;(B6+1),(YEAR((B6+1))-YEAR(MAX(B5,DATE(IF(MONTH(B6)&gt;=12,YEAR(B6),YEAR(B6)-1),12,1))))-1,(YEAR((B6+1))-YEAR(MAX(B5,DATE(IF(MONTH(B6)&gt;=12,YEAR(B6),YEAR(B6)-1),12,1)))))</f>
@@ -1948,13 +1987,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B16" s="16">
         <f>F10</f>
       </c>
       <c r="E16" s="12" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F16" s="21">
         <f>EDATE(MAX(B5,DATE(IF(MONTH(B6)&gt;=12,YEAR(B6),YEAR(B6)-1),12,1)),12*F15)</f>
@@ -1962,13 +2001,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B17" s="26">
         <f>F11</f>
       </c>
       <c r="E17" s="12" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F17" s="20">
         <f>MIN(12,IF(EDATE(F16,((YEAR((B6+1))-YEAR(F16))*12+MONTH((B6+1))-MONTH(F16)))&gt;(B6+1),((YEAR((B6+1))-YEAR(F16))*12+MONTH((B6+1))-MONTH(F16))-1,((YEAR((B6+1))-YEAR(F16))*12+MONTH((B6+1))-MONTH(F16))))</f>
@@ -1976,13 +2015,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B18" s="16">
         <f>F12</f>
       </c>
       <c r="E18" s="12" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F18" s="20">
         <f>(B6+1)-EDATE(F16,F17)</f>
@@ -1990,13 +2029,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B19" s="16">
         <f>F25</f>
       </c>
       <c r="E19" s="12" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F19" s="14">
         <f>MIN(12,F15*12+F17+F18/30)</f>
@@ -2004,13 +2043,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B20" s="16">
         <f>F26</f>
       </c>
       <c r="E20" s="12" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F20" s="20">
         <f>IF(EDATE(MAX(B5,DATE(IF(MONTH(B6)&gt;=INDEX('Tablas oficiales'!$C$28:$C$29,MATCH(B9,'Tablas oficiales'!$B$28:$B$29,0)),YEAR(B6),YEAR(B6)-1),INDEX('Tablas oficiales'!$C$28:$C$29,MATCH(B9,'Tablas oficiales'!$B$28:$B$29,0)),1)),12*(YEAR((B6+1))-YEAR(MAX(B5,DATE(IF(MONTH(B6)&gt;=INDEX('Tablas oficiales'!$C$28:$C$29,MATCH(B9,'Tablas oficiales'!$B$28:$B$29,0)),YEAR(B6),YEAR(B6)-1),INDEX('Tablas oficiales'!$C$28:$C$29,MATCH(B9,'Tablas oficiales'!$B$28:$B$29,0)),1)))))&gt;(B6+1),(YEAR((B6+1))-YEAR(MAX(B5,DATE(IF(MONTH(B6)&gt;=INDEX('Tablas oficiales'!$C$28:$C$29,MATCH(B9,'Tablas oficiales'!$B$28:$B$29,0)),YEAR(B6),YEAR(B6)-1),INDEX('Tablas oficiales'!$C$28:$C$29,MATCH(B9,'Tablas oficiales'!$B$28:$B$29,0)),1))))-1,(YEAR((B6+1))-YEAR(MAX(B5,DATE(IF(MONTH(B6)&gt;=INDEX('Tablas oficiales'!$C$28:$C$29,MATCH(B9,'Tablas oficiales'!$B$28:$B$29,0)),YEAR(B6),YEAR(B6)-1),INDEX('Tablas oficiales'!$C$28:$C$29,MATCH(B9,'Tablas oficiales'!$B$28:$B$29,0)),1)))))</f>
@@ -2018,13 +2057,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B21" s="16">
         <f>F31</f>
       </c>
       <c r="E21" s="12" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F21" s="21">
         <f>EDATE(MAX(B5,DATE(IF(MONTH(B6)&gt;=INDEX('Tablas oficiales'!$C$28:$C$29,MATCH(B9,'Tablas oficiales'!$B$28:$B$29,0)),YEAR(B6),YEAR(B6)-1),INDEX('Tablas oficiales'!$C$28:$C$29,MATCH(B9,'Tablas oficiales'!$B$28:$B$29,0)),1)),12*F20)</f>
@@ -2032,13 +2071,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B22" s="18">
         <f>ROUND(F10+F12+F25+F26+F31,2)</f>
       </c>
       <c r="E22" s="12" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F22" s="20">
         <f>MIN(12,IF(EDATE(F21,((YEAR((B6+1))-YEAR(F21))*12+MONTH((B6+1))-MONTH(F21)))&gt;(B6+1),((YEAR((B6+1))-YEAR(F21))*12+MONTH((B6+1))-MONTH(F21))-1,((YEAR((B6+1))-YEAR(F21))*12+MONTH((B6+1))-MONTH(F21))))</f>
@@ -2046,7 +2085,7 @@
     </row>
     <row r="23" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E23" s="12" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F23" s="20">
         <f>(B6+1)-EDATE(F21,F22)</f>
@@ -2054,12 +2093,12 @@
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="E24" s="12" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F24" s="14">
         <f>MIN(12,F20*12+F22+F23/30)</f>
@@ -2067,7 +2106,7 @@
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E25" s="12" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F25" s="13">
         <f>IF(B10="Sí",0,ROUND(B7*F19/12,2))</f>
@@ -2075,7 +2114,7 @@
     </row>
     <row r="26" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E26" s="12" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F26" s="13">
         <f>IF(B10="Sí",0,ROUND('Tablas oficiales'!$C$27*F24/12,2))</f>
@@ -2083,12 +2122,12 @@
     </row>
     <row r="28" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E28" s="10" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E29" s="12" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F29" s="20">
         <f>'Tablas oficiales'!$C$34+MIN(MAX(F4+1-'Tablas oficiales'!$C$35,0),'Tablas oficiales'!$C$36)</f>
@@ -2096,7 +2135,7 @@
     </row>
     <row r="30" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E30" s="12" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F30" s="14">
         <f>F29*((F6+F7/30)/12)</f>
@@ -2104,7 +2143,7 @@
     </row>
     <row r="31" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E31" s="12" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F31" s="13">
         <f>ROUND(F30*B7/30+B11*B7/30,2)</f>
@@ -2137,8 +2176,8 @@
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B8">
       <formula1>"Despido intempestivo (sin causa),Renuncia con aviso escrito (desahucio),Acuerdo entre las partes,Visto bueno pedido por el empleador"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B9">
-      <formula1>'Tablas oficiales'!$B$28:$B$29</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Región donde trabajabas)." sqref="B9">
+      <formula1>'Liquidación'!$Z$1:$Z$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2165,7 +2204,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -2176,7 +2215,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2187,219 +2226,219 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C4" s="30">
         <v>7</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>127</v>
+        <v>12</v>
       </c>
       <c r="C5" s="33">
         <v>9</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>128</v>
+        <v>14</v>
       </c>
       <c r="C6" s="30">
         <v>11</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
       <c r="C7" s="33">
         <v>14</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="C8" s="30">
         <v>17</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="C9" s="33">
         <v>20</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G9" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C10" s="30">
         <v>9.45</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
       <c r="D11" s="36" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G11" s="36" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
@@ -2544,108 +2583,108 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="32" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C24" s="33">
         <v>100</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E24" s="32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F24" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G24" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C25" s="42">
         <v>821.8</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G25" s="29" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C26" s="33">
         <v>18</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F26" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G26" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B27" s="29" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C27" s="42">
         <v>482</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G27" s="29" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>152</v>
+        <v>46</v>
       </c>
       <c r="C28" s="33">
         <v>3</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E28" s="32" t="s">
         <v>153</v>
@@ -2654,21 +2693,21 @@
         <v>154</v>
       </c>
       <c r="G28" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C29" s="30">
         <v>8</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E29" s="29" t="s">
         <v>153</v>
@@ -2677,7 +2716,7 @@
         <v>154</v>
       </c>
       <c r="G29" s="29" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2685,13 +2724,13 @@
         <v>155</v>
       </c>
       <c r="B30" s="32" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C30" s="33">
         <v>25</v>
       </c>
       <c r="D30" s="32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E30" s="32" t="s">
         <v>156</v>
@@ -2700,7 +2739,7 @@
         <v>157</v>
       </c>
       <c r="G30" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2708,7 +2747,7 @@
         <v>158</v>
       </c>
       <c r="B31" s="29" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C31" s="30">
         <v>3</v>
@@ -2723,7 +2762,7 @@
         <v>157</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2731,7 +2770,7 @@
         <v>161</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C32" s="33">
         <v>3</v>
@@ -2746,7 +2785,7 @@
         <v>157</v>
       </c>
       <c r="G32" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2754,7 +2793,7 @@
         <v>163</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C33" s="30">
         <v>25</v>
@@ -2769,7 +2808,7 @@
         <v>157</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2777,7 +2816,7 @@
         <v>164</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C34" s="33">
         <v>15</v>
@@ -2792,7 +2831,7 @@
         <v>157</v>
       </c>
       <c r="G34" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2800,7 +2839,7 @@
         <v>166</v>
       </c>
       <c r="B35" s="29" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C35" s="30">
         <v>5</v>
@@ -2815,7 +2854,7 @@
         <v>157</v>
       </c>
       <c r="G35" s="29" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2823,7 +2862,7 @@
         <v>167</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C36" s="33">
         <v>15</v>
@@ -2838,7 +2877,7 @@
         <v>157</v>
       </c>
       <c r="G36" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas, tu remuneración y cómo terminó la relación, y te dice el desahucio, la indemnización, los décimos pendientes y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -377,7 +377,7 @@
     <t>Tablas oficiales de Ecuador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1873,7 +1873,7 @@
         <v>82</v>
       </c>
       <c r="B6" s="22">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>83</v>

--- a/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ec/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: pones tus fechas, tu remuneración y cómo terminó la relación, y te dice el desahucio, la indemnización, los décimos pendientes y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 22/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -377,7 +377,7 @@
     <t>Tablas oficiales de Ecuador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 22/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1873,7 +1873,7 @@
         <v>82</v>
       </c>
       <c r="B6" s="22">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>83</v>
